--- a/AAII_Financials/Yearly/DARE_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/DARE_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="92">
   <si>
     <t>DARE</t>
   </si>
@@ -2975,7 +2975,7 @@
         <v>2100</v>
       </c>
       <c r="E58" s="3">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="F58" s="3">
         <v>500</v>
@@ -3125,10 +3125,10 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>600</v>
+        <v>5900</v>
       </c>
       <c r="E61" s="3">
-        <v>800</v>
+        <v>5500</v>
       </c>
       <c r="F61" s="3">
         <v>900</v>
@@ -3175,11 +3175,11 @@
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
-        <v>5400</v>
-      </c>
-      <c r="E62" s="3">
-        <v>4700</v>
+      <c r="D62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="F62" s="3">
         <v>3900</v>
